--- a/daily/2026-04-08.xlsx
+++ b/daily/2026-04-08.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -710,7 +728,6 @@
       <c r="V3" t="n">
         <v>6</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>51</v>
       </c>
@@ -1116,7 +1133,6 @@
       <c r="V8" t="n">
         <v>10</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>8</v>
       </c>
@@ -2178,7 +2194,6 @@
       <c r="V21" t="n">
         <v>16</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>4.6</v>
       </c>
@@ -2338,7 +2353,6 @@
       <c r="V23" t="n">
         <v>16</v>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>-15.9</v>
       </c>
@@ -2416,7 +2430,6 @@
       <c r="V24" t="n">
         <v>16</v>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>-3.4</v>
       </c>
@@ -2986,7 +2999,6 @@
       <c r="V31" t="n">
         <v>29</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>-16.6</v>
       </c>
@@ -3228,7 +3240,6 @@
       <c r="V34" t="n">
         <v>17</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-25.3</v>
       </c>
@@ -3306,7 +3317,6 @@
       <c r="V35" t="n">
         <v>9</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-11.9</v>
       </c>
@@ -3712,7 +3722,6 @@
       <c r="V40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>30.8</v>
       </c>
@@ -3872,7 +3881,6 @@
       <c r="V42" t="n">
         <v>9</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>2.5</v>
       </c>
@@ -4196,7 +4204,6 @@
       <c r="V46" t="n">
         <v>7</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>2.9</v>
       </c>
@@ -4848,7 +4855,6 @@
       <c r="V54" t="n">
         <v>3</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>-11.3</v>
       </c>
@@ -4926,7 +4932,6 @@
       <c r="V55" t="n">
         <v>3</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>-13.1</v>
       </c>
@@ -5004,7 +5009,6 @@
       <c r="V56" t="n">
         <v>18</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>-3.7</v>
       </c>
@@ -5656,7 +5660,6 @@
       <c r="V64" t="n">
         <v>18</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-8</v>
       </c>
@@ -5816,7 +5819,6 @@
       <c r="V66" t="n">
         <v>28</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>-3.6</v>
       </c>
@@ -10517,1523 +10519,3487 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 31 pts vs 24.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 35 played vs L10 avg 33.8. Shooting efficiency was hot: 63.2% FG (+19.0% vs L10 avg of 44.2%). 12/19 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, FG Trend. Projection model targeted 27.3 pts — actual 31 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Strus scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Strus played 21 min (-4.9 vs L10 avg of 26.1) — 19% less than expected. Shooting was in line with averages: 42.9% FG (3/7, L10 avg 43.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 9.3 pts — actual 8 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Strus in this role.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mobley scored 22 pts vs 17.5 line (+4.5), OVER hit by 4.5 pts. Mobley played 36 min (+5.5 vs L10 avg of 30.1) — 18% more than expected. Shooting efficiency was cold: 53.3% FG (-12.9% vs L10 avg of 66.2%). 8/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: Min Trend. Projection model targeted 18.4 pts — actual 22 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harden scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 35.3. Shooting efficiency was cold: 26.1% FG (-22.7% vs L10 avg of 48.8%). 6/23 from the field. Signals that called it correctly: Volume, Context, Defense, H2H, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 23.1 pts — actual 21 was 2.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Harden's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Kuminga scored 24 pts vs 10.5 line (+13.5), UNDER missed by 13.5 pts. Kuminga played 30 min (+10.4 vs L10 avg of 20.1) — 52% more than expected. Shooting efficiency was hot: 55.0% FG (+13.4% vs L10 avg of 41.6%). 11/20 from the field. Counter-signals that proved correct: Volume, Defense, H2H, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 9.5 pts — actual 24 was 14.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 12 pts vs 22.5 line (-10.5), OVER missed by 10.5 pts. Minutes were as expected: 34 played vs L10 avg 35.9. Shooting efficiency was cold: 25.0% FG (-22.8% vs L10 avg of 47.8%). 4/16 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend. Signals that were wrong: Volume, Context, Defense. Projection model targeted 23.4 pts — actual 12 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — McCollum scored 12 pts vs 18.5 line (-6.5), OVER missed by 6.5 pts. Minutes were as expected: 32 played vs L10 avg 29.9. Shooting efficiency was cold: 37.5% FG (-10.7% vs L10 avg of 48.2%). 6/16 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, Pace. Projection model targeted 22.6 pts — actual 12 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Okongwu scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. Okongwu played 33 min (+3.8 vs L10 avg of 29.1) — 13% more than expected. Shooting efficiency was hot: 70.0% FG (+24.6% vs L10 avg of 45.4%). 7/10 from the field. Counter-signals that proved correct: Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.6 pts — actual 18 was 6.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Alexander-Walker scored 25 pts vs 20.5 line (+4.5), UNDER missed by 4.5 pts. Alexander-Walker played 39 min (+5.5 vs L10 avg of 33.7) — 16% more than expected. Shooting was in line with averages: 52.6% FG (10/19, L10 avg 53.3%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Min Trend. Projection model targeted 19.8 pts — actual 25 was 5.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Alexander-Walker's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Allen scored 16 pts vs 14.5 line (+1.5), UNDER missed by 1.5 pts. Allen played 29 min (+3.2 vs L10 avg of 25.9) — 12% more than expected. Shooting efficiency was cold: 44.4% FG (-25.9% vs L10 avg of 70.3%). 4/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, Min Trend. Projection model targeted 13.6 pts — actual 16 was 2.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Daniels scored 12 pts vs 11.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 33 played vs L10 avg 32.4. Shooting efficiency was cold: 45.5% FG (-7.9% vs L10 avg of 53.4%). 5/11 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 10.2 pts — actual 12 was 1.8 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ATL @ CLE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Merrill scored 6 pts vs 9.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 27 played vs L10 avg 29.4. Shooting efficiency was hot: 66.7% FG (+23.4% vs L10 avg of 43.3%). 2/3 from the field. Signals that called it correctly: H2H (1/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.3 pts — actual 6 was 2.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Merrill's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 7 pts vs 11.5 line (-4.5), UNDER hit by 4.5 pts. Jr. played 19 min (-3.1 vs L10 avg of 22.2) — 14% less than expected. Shooting efficiency was cold: 25.0% FG (-9.6% vs L10 avg of 34.6%). 3/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 9.2 pts — actual 7 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Taurean Prince</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Prince scored 15 pts vs 9.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 28 played vs L10 avg 25.9. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 46.1%). Signals that called it correctly: Trend, H2H, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.2 pts — actual 15 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Prince in this role.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 10 pts vs 9.5 line (+0.5), UNDER missed by 0.5 pts. Thompson played 24 min (-4.6 vs L10 avg of 29.0) — 16% less than expected. Shooting efficiency was hot: 66.7% FG (+8.1% vs L10 avg of 58.6%). 4/6 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.9 pts — actual 10 was 2.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Thompson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Duren scored 21 pts vs 18.5 line (+2.5), UNDER missed by 2.5 pts. Duren played 28 min (-3.8 vs L10 avg of 31.4) — 12% less than expected. Shooting efficiency was hot: 88.9% FG (+22.0% vs L10 avg of 66.9%). 8/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 17.1 pts — actual 21 was 3.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Robinson scored 20 pts vs 10.5 line (+9.5), OVER hit by 9.5 pts. Minutes were as expected: 24 played vs L10 avg 27.1. Shooting efficiency was hot: 61.5% FG (+17.8% vs L10 avg of 43.7%). 8/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 10.6 pts — actual 20 was 9.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harris scored 10 pts vs 12.5 line (-2.5), UNDER hit by 2.5 pts. Harris played 23 min (-3.0 vs L10 avg of 26.1) — 11% less than expected. Shooting efficiency was cold: 37.5% FG (-15.3% vs L10 avg of 52.8%). 3/8 from the field. Signals that called it correctly: HR L30, Trend, Context, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 11.8 pts — actual 10 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Harris in this role.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Cade Cunningham</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>MIL @ DET</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Cunningham scored 13 pts vs 16.5 line (-3.5), OVER missed by 3.5 pts. Cunningham played 26 min (-5.6 vs L10 avg of 31.3) — 18% less than expected. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 51.1%). Counter-signals that proved correct: Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.6 pts — actual 13 was 6.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Cunningham for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 20 pts vs 22.5 line (-2.5), OVER missed by 2.5 pts. Banchero played 29 min (-5.7 vs L10 avg of 35.1) — 16% less than expected. Shooting efficiency was hot: 72.7% FG (+30.5% vs L10 avg of 42.2%). 8/11 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 29.4 pts — actual 20 was 9.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Banchero for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Bane scored 18 pts vs 19.5 line (-1.5), OVER missed by 1.5 pts. Bane played 30 min (-3.7 vs L10 avg of 33.4) — 11% less than expected. Shooting efficiency was hot: 53.8% FG (+8.7% vs L10 avg of 45.1%). 7/13 from the field. Counter-signals that proved correct: HR L10, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 26.7 pts — actual 18 was 8.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Franz Wagner</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wagner scored 17 pts vs 14.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 22 played vs L10 avg 22.5. Shooting efficiency was hot: 53.8% FG (+6.0% vs L10 avg of 47.8%). 7/13 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.6 pts — actual 17 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 11 pts vs 14.5 line (-3.5), UNDER hit by 3.5 pts. Suggs played 25 min (-5.9 vs L10 avg of 31.1) — 19% less than expected. Shooting efficiency was hot: 66.7% FG (+24.2% vs L10 avg of 42.5%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 11.9 pts — actual 11 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Suggs in this role.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 4 pts vs 11.5 line (-7.5), UNDER hit by 7.5 pts. Jr. played 20 min (-9.1 vs L10 avg of 28.7) — 32% less than expected. Shooting efficiency was cold: 40.0% FG (-18.0% vs L10 avg of 58.0%). 2/5 from the field. Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.7 pts — actual 4 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Anthony Black</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Black scored 7 pts vs 9.5 line (-2.5), UNDER hit by 2.5 pts. Black played 16 min (-10.5 vs L10 avg of 26.6) — 39% less than expected. Shooting efficiency was cold: 25.0% FG (-11.8% vs L10 avg of 36.8%). 1/4 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 1.8 pts — actual 7 was 5.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Black's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 12 pts vs 8.5 line (+3.5), OVER hit by 3.5 pts. Silva played 20 min (-7.9 vs L10 avg of 27.6) — 29% less than expected. Shooting efficiency was hot: 55.6% FG (+7.5% vs L10 avg of 48.1%). 5/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, FG Trend (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 11.5 pts — actual 12 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Silva in this role.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>WIN — DiVincenzo scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. DiVincenzo played 21 min (-9.7 vs L10 avg of 30.8) — 31% less than expected. Shooting efficiency was hot: 57.1% FG (+23.1% vs L10 avg of 34.0%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, Min Trend. Projection model targeted 6.4 pts — actual 12 was 5.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Reid scored 15 pts vs 16.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 24 played vs L10 avg 26.0. Shooting efficiency was hot: 54.5% FG (+17.3% vs L10 avg of 37.2%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 9.0 pts — actual 15 was 6.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Jaden McDaniels</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — McDaniels scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. McDaniels played 19 min (-11.2 vs L10 avg of 30.5) — 37% less than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 47.1%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 5.4 pts — actual 18 was 12.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag McDaniels for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Bones Hyland</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>MIN @ ORL</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Hyland scored 9 pts vs 17.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 23 played vs L10 avg 25.4. Shooting efficiency was cold: 37.5% FG (-5.1% vs L10 avg of 42.6%). 3/8 from the field. Signals that called it correctly: Volume, HR L30, Context, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.5 pts — actual 9 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hyland in this role.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Fox scored 25 pts vs 21.5 line (+3.5), UNDER missed by 3.5 pts. Fox played 34 min (+7.1 vs L10 avg of 27.4) — 26% more than expected. Shooting was in line with averages: 50.0% FG (10/20, L10 avg 49.0%). Counter-signals that proved correct: Defense, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.8 pts — actual 25 was 6.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 20 pts vs 14.5 line (+5.5), UNDER missed by 5.5 pts. Johnson played 29 min (+5.3 vs L10 avg of 23.6) — 22% more than expected. Shooting efficiency was hot: 53.3% FG (+6.5% vs L10 avg of 46.8%). 8/15 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.7 pts — actual 20 was 12.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 13 pts vs 17.5 line (-4.5), UNDER hit by 4.5 pts. Harper played 33 min (+8.3 vs L10 avg of 24.3) — 34% more than expected. Shooting efficiency was cold: 42.9% FG (-16.3% vs L10 avg of 59.2%). 6/14 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 8.2 pts — actual 13 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Harper's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Matisse Thybulle</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thybulle scored 0 pts vs 8.5 line (-8.5), UNDER hit by 8.5 pts. Minutes were as expected: 24 played vs L10 avg 22.0. Shooting efficiency was cold: 0.0% FG (-46.4% vs L10 avg of 46.4%). 0/5 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 5.7 pts — actual 0 was 5.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Thybulle's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 11 pts vs 12.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 28 played vs L10 avg 26.4. Shooting efficiency was hot: 57.1% FG (+8.2% vs L10 avg of 48.9%). 4/7 from the field. Signals that called it correctly: Trend, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.0 pts — actual 11 was 1.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clingan in this role.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Vassell scored 14 pts vs 16.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 29.6. Shooting efficiency was cold: 38.5% FG (-5.4% vs L10 avg of 43.9%). 5/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Min Trend. Projection model targeted 15.4 pts — actual 14 was 1.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Vassell in this role.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Avdija scored 29 pts vs 25.5 line (+3.5), UNDER missed by 3.5 pts. Avdija played 38 min (+5.2 vs L10 avg of 32.3) — 16% more than expected. Shooting efficiency was hot: 61.9% FG (+17.4% vs L10 avg of 44.5%). 13/21 from the field. Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.5 pts — actual 29 was 8.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. Camara played 40 min (+8.0 vs L10 avg of 32.0) — 25% more than expected. Shooting was in line with averages: 58.3% FG (7/12, L10 avg 53.8%). Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.4 pts — actual 18 was 4.6 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Camara's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 13 pts vs 18.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 31.1. Shooting efficiency was cold: 35.3% FG (-6.9% vs L10 avg of 42.2%). 6/17 from the field. Counter-signals that proved correct: Volume, HR L10, Context, Defense. Signals that were wrong: HR L30, Trend, Pace. Projection model targeted 23.7 pts — actual 13 was 10.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Henderson scored 20 pts vs 15.5 line (+4.5), UNDER missed by 4.5 pts. Henderson played 38 min (+12.3 vs L10 avg of 25.7) — 48% more than expected. Shooting efficiency was cold: 35.0% FG (-7.7% vs L10 avg of 42.7%). 7/20 from the field. Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.5 pts — actual 20 was 10.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>WIN — III scored 4 pts vs 7.5 line (-3.5), UNDER hit by 3.5 pts. III played 13 min (-5.2 vs L10 avg of 18.0) — 29% less than expected. Shooting efficiency was hot: 66.7% FG (+5.9% vs L10 avg of 60.8%). 2/3 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, Defense, H2H. Projection model targeted 4.5 pts — actual 4 was 0.5 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for III in this role.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Champagnie scored 2 pts vs 12.5 line (-10.5), OVER missed by 10.5 pts. Minutes were as expected: 27 played vs L10 avg 27.2. Shooting efficiency was cold: 16.7% FG (-28.1% vs L10 avg of 44.8%). 1/6 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Pace. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 14.1 pts — actual 2 was 12.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Harrison Barnes</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 9 pts vs 8.5 line (+0.5), UNDER missed by 0.5 pts. Barnes played 27 min (+6.1 vs L10 avg of 20.7) — 29% more than expected. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 47.6%). Counter-signals that proved correct: Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.7 pts — actual 9 was 0.3 pts close (wrong direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Luke Kornet</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>POR @ SAS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Kornet scored 10 pts vs 7.5 line (+2.5), OVER hit by 2.5 pts. Kornet played 26 min (+6.3 vs L10 avg of 19.7) — 32% more than expected. Shooting efficiency was hot: 83.3% FG (+32.8% vs L10 avg of 50.5%). 5/6 from the field. Signals that called it correctly: Trend, Defense, H2H, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.1 pts — actual 10 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Kornet in this role.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gordon scored 6 pts vs 15.5 line (-9.5), OVER missed by 9.5 pts. Gordon played 22 min (-6.7 vs L10 avg of 29.0) — 23% less than expected. Shooting efficiency was cold: 33.3% FG (-12.6% vs L10 avg of 45.9%). 2/6 from the field. Counter-signals that proved correct: HR L10, Trend, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 26.0 pts — actual 6 was 20.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Gordon for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Murray scored 26 pts vs 24.5 line (+1.5), UNDER missed by 1.5 pts. Murray played 35 min (-3.8 vs L10 avg of 38.6) — 10% less than expected. Shooting was in line with averages: 47.1% FG (8/17, L10 avg 50.6%). Counter-signals that proved correct: Volume, Defense, Pace, FG Trend. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 21.4 pts — actual 26 was 4.6 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jokić scored 14 pts vs 24.5 line (-10.5), UNDER hit by 10.5 pts. Jokić played 31 min (-6.9 vs L10 avg of 37.9) — 18% less than expected. Shooting efficiency was hot: 62.5% FG (+6.7% vs L10 avg of 55.8%). 5/8 from the field. Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.8 pts — actual 14 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jokić's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 18 pts vs 12.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 30 played vs L10 avg 31.1. Shooting efficiency was hot: 66.7% FG (+15.6% vs L10 avg of 51.1%). 8/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context. Projection model targeted 12.2 pts — actual 18 was 5.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 13 pts vs 8.5 line (+4.5), UNDER missed by 4.5 pts. Brown played 26 min (+4.9 vs L10 avg of 21.2) — 23% more than expected. Shooting efficiency was hot: 71.4% FG (+26.8% vs L10 avg of 44.6%). 5/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 6.6 pts — actual 13 was 6.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Braun scored 14 pts vs 12.5 line (+1.5), OVER hit by 1.5 pts. Braun played 27 min (-5.8 vs L10 avg of 32.4) — 18% less than expected. Shooting efficiency was hot: 70.0% FG (+14.1% vs L10 avg of 55.9%). 7/10 from the field. Signals that called it correctly: Volume, Trend, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Min Trend. Projection model targeted 14.8 pts — actual 14 was 0.8 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Braun in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 13 pts vs 11.5 line (+1.5), UNDER missed by 1.5 pts. Jr. played 20 min (-4.6 vs L10 avg of 24.1) — 19% less than expected. Shooting efficiency was hot: 50.0% FG (+11.6% vs L10 avg of 38.4%). 5/10 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 10.9 pts — actual 13 was 2.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Taylor Hendricks</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hendricks scored 16 pts vs 9.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 22 played vs L10 avg 23.9. Shooting efficiency was hot: 75.0% FG (+31.3% vs L10 avg of 43.7%). 6/8 from the field. Counter-signals that proved correct: HR L10, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 8.3 pts — actual 16 was 7.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Coward scored 27 pts vs 14.5 line (+12.5), UNDER missed by 12.5 pts. Minutes were as expected: 22 played vs L10 avg 24.7. Shooting efficiency was hot: 58.8% FG (+11.5% vs L10 avg of 47.3%). 10/17 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.8 pts — actual 27 was 19.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Walter Clayton Jr.</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>MEM @ DEN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 15 pts vs 11.5 line (+3.5), UNDER missed by 3.5 pts. Jr. played 22 min (-3.5 vs L10 avg of 25.4) — 14% less than expected. Shooting efficiency was hot: 50.0% FG (+12.3% vs L10 avg of 37.7%). 5/10 from the field. Counter-signals that proved correct: Trend, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.1 pts — actual 15 was 9.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Cooper Flagg</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Flagg scored 11 pts vs 28.5 line (-17.5), UNDER hit by 17.5 pts. Flagg played 32 min (-3.9 vs L10 avg of 35.8) — 11% less than expected. Shooting efficiency was cold: 22.2% FG (-23.6% vs L10 avg of 45.8%). 4/18 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 23.6 pts — actual 11 was 12.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Flagg's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Jordan Goodwin</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Goodwin scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Goodwin played 13 min (-12.4 vs L10 avg of 25.5) — 49% less than expected. Shooting was in line with averages: 42.9% FG (3/7, L10 avg 45.8%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 4.9 pts — actual 9 was 4.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Goodwin's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brooks scored 28 pts vs 18.5 line (+9.5), UNDER missed by 9.5 pts. Brooks played 33 min (+5.3 vs L10 avg of 28.1) — 19% more than expected. Shooting efficiency was hot: 50.0% FG (+13.6% vs L10 avg of 36.4%). 11/22 from the field. Counter-signals that proved correct: Volume, HR L30, Defense, Pace. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 15.9 pts — actual 28 was 12.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 0 pts vs 20.5 line (-20.5), OVER missed by 20.5 pts. Green played 4 min (-25.9 vs L10 avg of 29.7) — 87% less than expected. Shooting efficiency was cold: 0.0% FG (-46.7% vs L10 avg of 46.7%). 0/2 from the field. Counter-signals that proved correct: Volume, HR L30, Context. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 20.6 pts — actual 0 was 20.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Green for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Booker scored 37 pts vs 26.5 line (+10.5), UNDER missed by 10.5 pts. Booker played 37 min (+3.6 vs L10 avg of 33.4) — 11% more than expected. Shooting was in line with averages: 48.1% FG (13/27, L10 avg 45.7%). Counter-signals that proved correct: HR L30, Trend, Defense, Pace. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 19.7 pts — actual 37 was 17.3 pts off (correct direction). Loss classification: BLOWOUT_EFFECT. Note: Game script invalidated the prop. Consider blowout probability when PHX is involved.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E62" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gillespie scored 13 pts vs 9.5 line (+3.5), UNDER missed by 3.5 pts. Gillespie played 34 min (+7.0 vs L10 avg of 26.8) — 26% more than expected. Shooting efficiency was hot: 41.7% FG (+8.3% vs L10 avg of 33.4%). 5/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 3.7 pts — actual 13 was 9.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Marvin Bagley III</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E63" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — III scored 20 pts vs 11.5 line (+8.5), UNDER missed by 8.5 pts. III played 26 min (+5.4 vs L10 avg of 20.9) — 26% more than expected. Shooting efficiency was hot: 72.7% FG (+12.1% vs L10 avg of 60.6%). 8/11 from the field. Counter-signals that proved correct: Trend, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.8 pts — actual 20 was 11.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Khris Middleton</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>DAL @ PHX</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Middleton scored 4 pts vs 10.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 18 played vs L10 avg 17.5. Shooting efficiency was cold: 0.0% FG (-31.9% vs L10 avg of 31.9%). 0/5 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (8/10 aligned). Counter-signals that were wrong: Volume, H2H. Projection model targeted 3.0 pts — actual 4 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>29.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Gilgeous-Alexander scored 20 pts vs 29.5 line (-9.5), UNDER hit by 9.5 pts. Minutes were as expected: 30 played vs L10 avg 31.2. Shooting efficiency was cold: 52.9% FG (-10.1% vs L10 avg of 63.0%). 9/17 from the field. Signals that called it correctly: HR L10, Trend, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 28.1 pts — actual 20 was 8.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Gilgeous-Alexander's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Leonard scored 20 pts vs 25.5 line (-5.5), OVER missed by 5.5 pts. Minutes were as expected: 30 played vs L10 avg 30.5. Shooting efficiency was cold: 44.4% FG (-9.4% vs L10 avg of 53.8%). 8/18 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 25.5 pts — actual 20 was 5.5 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Williams scored 18 pts vs 16.5 line (+1.5), OVER hit by 1.5 pts. Williams played 32 min (+8.7 vs L10 avg of 23.7) — 37% more than expected. Shooting efficiency was hot: 58.3% FG (+8.9% vs L10 avg of 49.4%). 7/12 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Pace. Projection model targeted 16.4 pts — actual 18 was 1.6 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williams in this role.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holmgren scored 30 pts vs 14.5 line (+15.5), UNDER missed by 15.5 pts. Holmgren played 31 min (+5.0 vs L10 avg of 26.2) — 19% more than expected. Shooting efficiency was hot: 76.9% FG (+23.4% vs L10 avg of 53.5%). 10/13 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 13.0 pts — actual 30 was 17.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 7 pts vs 10.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 24 played vs L10 avg 23.3. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 47.6%). Signals that called it correctly: HR L10, Trend, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.1 pts — actual 7 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mitchell in this role.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Lopez scored 16 pts vs 9.5 line (+6.5), UNDER missed by 6.5 pts. Lopez played 30 min (+3.0 vs L10 avg of 27.4) — 11% more than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 48.0%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, H2H. Projection model targeted 7.8 pts — actual 16 was 8.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Lopez's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 11 pts vs 8.5 line (+2.5), OVER hit by 2.5 pts. Jr. played 30 min (+3.3 vs L10 avg of 27.0) — 12% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 45.9%). Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 8.9 pts — actual 11 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Dunn scored 3 pts vs 7.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 27 played vs L10 avg 25.8. Shooting efficiency was cold: 14.3% FG (-27.5% vs L10 avg of 41.8%). 1/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: H2H. Projection model targeted 7.2 pts — actual 3 was 4.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Dort scored 6 pts vs 6.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 20 played vs L10 avg 21.3. Shooting efficiency was hot: 50.0% FG (+11.3% vs L10 avg of 38.7%). 2/4 from the field. Counter-signals that proved correct: HR L10, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 8.7 pts — actual 6 was 2.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hartenstein scored 10 pts vs 6.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 20 played vs L10 avg 20.4. Shooting efficiency was hot: 80.0% FG (+37.7% vs L10 avg of 42.3%). 4/5 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.6 pts — actual 10 was 3.4 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Jordan Miller</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Miller scored 16 pts vs 9.5 line (+6.5), UNDER missed by 6.5 pts. Miller played 30 min (+6.6 vs L10 avg of 23.0) — 29% more than expected. Shooting was in line with averages: 54.5% FG (6/11, L10 avg 56.0%). Counter-signals that proved correct: Volume, HR L30, HR L10, FG Trend. Signals that were wrong: Trend, Context, Defense. Projection model targeted 5.2 pts — actual 16 was 10.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Miller's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Wallace scored 3 pts vs 6.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 21 played vs L10 avg 22.8. Shooting efficiency was cold: 16.7% FG (-30.8% vs L10 avg of 47.5%). 1/6 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 7.6 pts — actual 3 was 4.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>OKC @ LAC</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>12.5</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Collins scored 12 pts vs 12.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 27 played vs L10 avg 26.6. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 50.3%). Counter-signals that proved correct: Defense, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.5 pts — actual 12 was 4.5 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-09 12:01</t>
+        </is>
       </c>
     </row>
   </sheetData>
